--- a/基础数据.xlsx
+++ b/基础数据.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32420" windowHeight="14860"/>
+    <workbookView windowHeight="14860" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="科技管理应用" sheetId="1" r:id="rId1"/>
+    <sheet name="巡查问题在线管理" sheetId="2" r:id="rId2"/>
+    <sheet name="项目管理应用" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="140">
   <si>
     <t>b级节点</t>
   </si>
@@ -264,6 +266,189 @@
   </si>
   <si>
     <t>专著</t>
+  </si>
+  <si>
+    <t>巡查问题在线管理</t>
+  </si>
+  <si>
+    <t>人才信息管理</t>
+  </si>
+  <si>
+    <t>人才基本信息</t>
+  </si>
+  <si>
+    <t>人员姓名</t>
+  </si>
+  <si>
+    <t>人员编码</t>
+  </si>
+  <si>
+    <t>工作单位</t>
+  </si>
+  <si>
+    <t>出生年月</t>
+  </si>
+  <si>
+    <t>性别</t>
+  </si>
+  <si>
+    <t>籍贯</t>
+  </si>
+  <si>
+    <t>工作经历</t>
+  </si>
+  <si>
+    <t>专业培训信息</t>
+  </si>
+  <si>
+    <t>培训名称</t>
+  </si>
+  <si>
+    <t>主办单位</t>
+  </si>
+  <si>
+    <t>课程名称</t>
+  </si>
+  <si>
+    <t>考试层级</t>
+  </si>
+  <si>
+    <t>工作经历信息</t>
+  </si>
+  <si>
+    <t>任务级别</t>
+  </si>
+  <si>
+    <t>任务大类</t>
+  </si>
+  <si>
+    <t>任务名称</t>
+  </si>
+  <si>
+    <t>任务对象</t>
+  </si>
+  <si>
+    <t>人才库管理</t>
+  </si>
+  <si>
+    <t>入库信息填报</t>
+  </si>
+  <si>
+    <t>人才库编码</t>
+  </si>
+  <si>
+    <t>入库时间</t>
+  </si>
+  <si>
+    <t>人才大类</t>
+  </si>
+  <si>
+    <t>入库详情</t>
+  </si>
+  <si>
+    <t>查看</t>
+  </si>
+  <si>
+    <t>任务管理</t>
+  </si>
+  <si>
+    <t>新建</t>
+  </si>
+  <si>
+    <t>任务编码</t>
+  </si>
+  <si>
+    <t>任务类型</t>
+  </si>
+  <si>
+    <t>任务小类</t>
+  </si>
+  <si>
+    <t>任务内容</t>
+  </si>
+  <si>
+    <t>组队选才</t>
+  </si>
+  <si>
+    <t>工作组名称</t>
+  </si>
+  <si>
+    <t>工作组编号</t>
+  </si>
+  <si>
+    <t>生成初选名单</t>
+  </si>
+  <si>
+    <t>关联任务</t>
+  </si>
+  <si>
+    <t>问题管理</t>
+  </si>
+  <si>
+    <t>问题下发</t>
+  </si>
+  <si>
+    <t>问题名称</t>
+  </si>
+  <si>
+    <t>问题类型</t>
+  </si>
+  <si>
+    <t>涉及单位</t>
+  </si>
+  <si>
+    <t>预计完成时间</t>
+  </si>
+  <si>
+    <t>问题整改</t>
+  </si>
+  <si>
+    <t>整改措施</t>
+  </si>
+  <si>
+    <t>整改成效</t>
+  </si>
+  <si>
+    <t>项目管理应用</t>
+  </si>
+  <si>
+    <t>立项管理</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>项目变更</t>
+  </si>
+  <si>
+    <t>变更内容</t>
+  </si>
+  <si>
+    <t>交付物管理</t>
+  </si>
+  <si>
+    <t>交付物名称</t>
+  </si>
+  <si>
+    <t>上传</t>
+  </si>
+  <si>
+    <t>里程碑计划</t>
+  </si>
+  <si>
+    <t>计划完成时间</t>
+  </si>
+  <si>
+    <t>上传时间</t>
+  </si>
+  <si>
+    <t>填报</t>
+  </si>
+  <si>
+    <t>验收时间</t>
+  </si>
+  <si>
+    <t>项目进度</t>
   </si>
 </sst>
 </file>
@@ -630,7 +815,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -648,6 +833,43 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -777,7 +999,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -789,34 +1011,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -901,20 +1123,29 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1442,7 +1673,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="16.0192307692308" customWidth="1"/>
@@ -1486,10 +1717,10 @@
       <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1498,10 +1729,10 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1510,10 +1741,10 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1522,10 +1753,10 @@
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1534,60 +1765,60 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="2"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="2"/>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="2"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="2"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="2"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1"/>
@@ -1596,10 +1827,10 @@
       <c r="D12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1608,10 +1839,10 @@
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1620,10 +1851,10 @@
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1632,10 +1863,10 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="2"/>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1"/>
@@ -1644,10 +1875,10 @@
       <c r="D16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1656,10 +1887,10 @@
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1668,10 +1899,10 @@
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1680,10 +1911,10 @@
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1694,10 +1925,10 @@
       <c r="D20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1706,10 +1937,10 @@
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1720,10 +1951,10 @@
       <c r="D22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="3" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1732,10 +1963,10 @@
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1744,10 +1975,10 @@
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="2"/>
+      <c r="F24" s="3"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1"/>
@@ -1758,10 +1989,10 @@
       <c r="D25" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1770,10 +2001,10 @@
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="3" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1782,10 +2013,10 @@
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1794,10 +2025,10 @@
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1806,10 +2037,10 @@
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1818,10 +2049,10 @@
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="3" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1830,10 +2061,10 @@
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1842,10 +2073,10 @@
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1858,10 +2089,10 @@
       <c r="D33" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1870,10 +2101,10 @@
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="5" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1882,10 +2113,10 @@
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1894,10 +2125,10 @@
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1906,10 +2137,10 @@
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F37" s="2"/>
+      <c r="F37" s="3"/>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1"/>
@@ -1918,10 +2149,10 @@
       <c r="D38" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="3" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1930,10 +2161,10 @@
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="3" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1944,8 +2175,8 @@
       <c r="D40" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2" t="s">
+      <c r="E40" s="3"/>
+      <c r="F40" s="3" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1954,8 +2185,8 @@
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2" t="s">
+      <c r="E41" s="3"/>
+      <c r="F41" s="3" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1966,10 +2197,10 @@
       <c r="D42" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1978,8 +2209,8 @@
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2" t="s">
+      <c r="E43" s="3"/>
+      <c r="F43" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1987,13 +2218,13 @@
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2001,13 +2232,13 @@
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="3" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2020,10 +2251,10 @@
       <c r="D46" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="3" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2032,10 +2263,10 @@
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="3" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2044,40 +2275,40 @@
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F48" s="2"/>
+      <c r="F48" s="3"/>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F49" s="2"/>
+      <c r="F49" s="3"/>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F50" s="2"/>
+      <c r="F50" s="3"/>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F51" s="2"/>
+      <c r="F51" s="3"/>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1"/>
@@ -2086,10 +2317,10 @@
       <c r="D52" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="3" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2098,39 +2329,896 @@
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
-      <c r="E53" s="2" t="s">
+      <c r="E53" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F53" s="2"/>
+      <c r="F53" s="3"/>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
-      <c r="E54" s="2" t="s">
+      <c r="E54" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F54" s="2"/>
+      <c r="F54" s="3"/>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
-      <c r="E55" s="2" t="s">
+      <c r="E55" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F55" s="2"/>
+      <c r="F55" s="3"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F60" s="3"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F61" s="3"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F62" s="3"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F77" s="3"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F78" s="3"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F79" s="3"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F80" s="3"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F85" s="3"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F89" s="3"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="4"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="4"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="4"/>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" s="4"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F104" s="3"/>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="4"/>
+      <c r="B105" s="4"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F105" s="3"/>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="4"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="4"/>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="4"/>
+      <c r="B110" s="4"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="4"/>
+      <c r="B111" s="4"/>
+      <c r="C111" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="4"/>
+      <c r="B112" s="4"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="4"/>
+      <c r="B113" s="4"/>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="4"/>
+      <c r="B114" s="4"/>
+      <c r="C114" s="6"/>
+      <c r="D114" s="6"/>
+      <c r="E114" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" s="4"/>
+      <c r="B115" s="4"/>
+      <c r="C115" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" s="4"/>
+      <c r="B116" s="4"/>
+      <c r="C116" s="4"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" s="4"/>
+      <c r="B117" s="4"/>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" s="4"/>
+      <c r="B118" s="4"/>
+      <c r="C118" s="4"/>
+      <c r="D118" s="4"/>
+      <c r="E118" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" s="4"/>
+      <c r="B119" s="4"/>
+      <c r="C119" s="6"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" s="4"/>
+      <c r="B120" s="4"/>
+      <c r="C120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" s="4"/>
+      <c r="B121" s="4"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" s="4"/>
+      <c r="B122" s="4"/>
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
+      <c r="E122" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" s="4"/>
+      <c r="B123" s="4"/>
+      <c r="C123" s="4"/>
+      <c r="D123" s="4"/>
+      <c r="E123" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" s="6"/>
+      <c r="B124" s="6"/>
+      <c r="C124" s="6"/>
+      <c r="D124" s="6"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="45">
     <mergeCell ref="A2:A55"/>
+    <mergeCell ref="A56:A98"/>
+    <mergeCell ref="A99:A124"/>
     <mergeCell ref="B2:B55"/>
+    <mergeCell ref="B56:B98"/>
+    <mergeCell ref="B99:B124"/>
     <mergeCell ref="C2:C24"/>
     <mergeCell ref="C25:C32"/>
     <mergeCell ref="C33:C45"/>
     <mergeCell ref="C46:C55"/>
+    <mergeCell ref="C56:C70"/>
+    <mergeCell ref="C71:C80"/>
+    <mergeCell ref="C81:C89"/>
+    <mergeCell ref="C90:C98"/>
+    <mergeCell ref="C99:C105"/>
+    <mergeCell ref="C106:C110"/>
+    <mergeCell ref="C111:C114"/>
+    <mergeCell ref="C115:C119"/>
+    <mergeCell ref="C120:C124"/>
     <mergeCell ref="D2:D11"/>
     <mergeCell ref="D12:D15"/>
     <mergeCell ref="D16:D19"/>
@@ -2143,6 +3231,974 @@
     <mergeCell ref="D42:D43"/>
     <mergeCell ref="D46:D51"/>
     <mergeCell ref="D52:D55"/>
+    <mergeCell ref="D56:D62"/>
+    <mergeCell ref="D63:D66"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="D71:D75"/>
+    <mergeCell ref="D76:D80"/>
+    <mergeCell ref="D81:D85"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="D94:D98"/>
+    <mergeCell ref="D99:D105"/>
+    <mergeCell ref="D106:D110"/>
+    <mergeCell ref="D111:D114"/>
+    <mergeCell ref="D115:D119"/>
+    <mergeCell ref="D120:D124"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="2" width="18.1057692307692" customWidth="1"/>
+    <col min="3" max="3" width="16.3365384615385" customWidth="1"/>
+    <col min="4" max="4" width="29.6442307692308" customWidth="1"/>
+    <col min="5" max="5" width="34.9326923076923" customWidth="1"/>
+    <col min="6" max="6" width="34.7692307692308" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F31" s="3"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F35" s="3"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A2:A44"/>
+    <mergeCell ref="B2:B44"/>
+    <mergeCell ref="C2:C16"/>
+    <mergeCell ref="C17:C26"/>
+    <mergeCell ref="C27:C35"/>
+    <mergeCell ref="C36:C44"/>
+    <mergeCell ref="D2:D8"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="D22:D26"/>
+    <mergeCell ref="D27:D31"/>
+    <mergeCell ref="D32:D35"/>
+    <mergeCell ref="D36:D39"/>
+    <mergeCell ref="D40:D44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="16.6634615384615" customWidth="1"/>
+    <col min="3" max="3" width="17.7788461538462" customWidth="1"/>
+    <col min="4" max="4" width="17.1442307692308" customWidth="1"/>
+    <col min="5" max="5" width="20.9903846153846" customWidth="1"/>
+    <col min="6" max="6" width="18.9038461538462" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A2:A27"/>
+    <mergeCell ref="B2:B27"/>
+    <mergeCell ref="C2:C8"/>
+    <mergeCell ref="C9:C13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="C18:C22"/>
+    <mergeCell ref="C23:C27"/>
+    <mergeCell ref="D2:D8"/>
+    <mergeCell ref="D9:D13"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="D18:D22"/>
+    <mergeCell ref="D23:D27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
